--- a/reports/2026-03-12.xlsx
+++ b/reports/2026-03-12.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-12 05:21 UTC</t>
+          <t>2026-03-12 17:03 UTC</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-12_1773292796580</t>
+          <t>2026-03-12_1773334934529</t>
         </is>
       </c>
     </row>
@@ -950,10 +950,10 @@
         <v>2.45315514862892</v>
       </c>
       <c r="P2" t="n">
-        <v>2.559</v>
+        <v>2.632</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.314641551727294</v>
+        <v>7.290401158322091</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
         <v>1.169138388750603</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03907013088493416</v>
+        <v>0.03795786676788346</v>
       </c>
       <c r="Z2" t="n">
-        <v>26143.65777</v>
+        <v>20517.44131</v>
       </c>
       <c r="AA2" t="n">
-        <v>31841.42116</v>
+        <v>25619.93872</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.241794</v>
+        <v>10.398214</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.557742</v>
+        <v>26.382778</v>
       </c>
       <c r="AD2" t="n">
-        <v>1404294790.341058</v>
+        <v>1448939419.602685</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COMPUSDT</t>
+          <t>DEEPUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Compound</t>
+          <t>DeepBook Protocol</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1038,19 +1038,15 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>78.17</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>78.17</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>none</t>
@@ -1065,54 +1061,54 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>17.79485789424142</v>
+        <v>0.02835889643807475</v>
       </c>
       <c r="P3" t="n">
-        <v>17.64</v>
+        <v>0.034508</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.8702395667432139</v>
+        <v>21.68315532077418</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>15.20598395089455</v>
+        <v>0.02256969868462025</v>
       </c>
       <c r="T3" t="n">
-        <v>14.54843842380249</v>
+        <v>20.41404455245976</v>
       </c>
       <c r="U3" t="n">
-        <v>19.57434368366556</v>
+        <v>0.03119478608188223</v>
       </c>
       <c r="V3" t="n">
-        <v>21.3538294730897</v>
+        <v>0.0340306757256897</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6873589940511522</v>
+        <v>0.4898588309779638</v>
       </c>
       <c r="X3" t="n">
-        <v>1.374717988102303</v>
+        <v>0.9797176619559265</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05670541536717643</v>
+        <v>0.06376996434679609</v>
       </c>
       <c r="Z3" t="n">
-        <v>10768.84935</v>
+        <v>30662.00613367</v>
       </c>
       <c r="AA3" t="n">
-        <v>4087.50564</v>
+        <v>30653.81337493</v>
       </c>
       <c r="AB3" t="n">
-        <v>60.043617</v>
+        <v>35.673139</v>
       </c>
       <c r="AC3" t="n">
-        <v>3310.49088</v>
+        <v>53.567102</v>
       </c>
       <c r="AD3" t="n">
-        <v>175945116.4988256</v>
+        <v>169919316.72061</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1127,12 +1123,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RONUSDT</t>
+          <t>ILVUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronin</t>
+          <t>Illuvium</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1142,7 +1138,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1156,10 +1152,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>76.11</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>76.11</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1183,54 +1179,54 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09716075239137541</v>
+        <v>3.761873902329719</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09922</v>
+        <v>4.255</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.119423283518529</v>
+        <v>13.10852278607451</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.07606081779442495</v>
+        <v>3.153853029240997</v>
       </c>
       <c r="T4" t="n">
-        <v>21.71652038258961</v>
+        <v>16.16271275632539</v>
       </c>
       <c r="U4" t="n">
-        <v>0.106876827630513</v>
+        <v>4.138061292562691</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1165929028696505</v>
+        <v>4.514248682795662</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4604789268181805</v>
+        <v>0.6187080195486644</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9209578536363604</v>
+        <v>1.237416039097327</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2725758417041102</v>
+        <v>0.3054870168017836</v>
       </c>
       <c r="Z4" t="n">
-        <v>13479.5500922</v>
+        <v>4615.6894405</v>
       </c>
       <c r="AA4" t="n">
-        <v>6364.6145002</v>
+        <v>1840.3309712</v>
       </c>
       <c r="AB4" t="n">
-        <v>41.282694</v>
+        <v>122.504139</v>
       </c>
       <c r="AC4" t="n">
-        <v>3035.18841</v>
+        <v>1459.267834</v>
       </c>
       <c r="AD4" t="n">
-        <v>76511023.35495403</v>
+        <v>29125629.62737596</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1245,12 +1241,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BERAUSDT</t>
+          <t>SPKUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Berachain</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1260,7 +1256,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1274,19 +1270,15 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>74.64</v>
+        <v>79.22</v>
       </c>
       <c r="I5" t="n">
-        <v>74.64</v>
+        <v>79.22</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>none</t>
@@ -1301,54 +1293,54 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5721818231782297</v>
+        <v>0.02068289975236165</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5783</v>
+        <v>0.02307</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.069271440289099</v>
+        <v>11.5414196085623</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.439897939688523</v>
+        <v>0.0174553083569267</v>
       </c>
       <c r="T5" t="n">
-        <v>23.1192040940632</v>
+        <v>15.60512033650605</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6294000054960528</v>
+        <v>0.02275118972759782</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6866181878138756</v>
+        <v>0.02481947970283398</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4325408417743897</v>
+        <v>0.6408153083322514</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8650816835487777</v>
+        <v>1.281630616664502</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08642295393655604</v>
+        <v>0.04337453914551982</v>
       </c>
       <c r="Z5" t="n">
-        <v>5256.71059</v>
+        <v>122.2521477</v>
       </c>
       <c r="AA5" t="n">
-        <v>5282.937331</v>
+        <v>600.4083439000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>47.425813</v>
+        <v>4002.279124</v>
       </c>
       <c r="AC5" t="n">
-        <v>136.20129</v>
+        <v>10981.199497</v>
       </c>
       <c r="AD5" t="n">
-        <v>132616738.3412393</v>
+        <v>56821501.96896987</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1363,12 +1355,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RENDERUSDT</t>
+          <t>COMPUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1378,7 +1370,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1392,15 +1384,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.12</v>
+        <v>78.17</v>
       </c>
       <c r="I6" t="n">
-        <v>71.12</v>
+        <v>78.17</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>none</t>
@@ -1415,54 +1411,54 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.420042038029597</v>
+        <v>17.79485789424142</v>
       </c>
       <c r="P6" t="n">
-        <v>1.511</v>
+        <v>17.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.405300655508284</v>
+        <v>0.4222686475226167</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1.185862664759147</v>
+        <v>15.20598395089455</v>
       </c>
       <c r="T6" t="n">
-        <v>16.49101695576489</v>
+        <v>14.54843842380249</v>
       </c>
       <c r="U6" t="n">
-        <v>1.562046241832557</v>
+        <v>19.57434368366556</v>
       </c>
       <c r="V6" t="n">
-        <v>1.704050445635516</v>
+        <v>21.3538294730897</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6063907415063466</v>
+        <v>0.6873589940511522</v>
       </c>
       <c r="X6" t="n">
-        <v>1.212781483012692</v>
+        <v>1.374717988102303</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0662471016893085</v>
+        <v>0.05603810591202894</v>
       </c>
       <c r="Z6" t="n">
-        <v>125606.91817</v>
+        <v>6609.15855</v>
       </c>
       <c r="AA6" t="n">
-        <v>154654.50956</v>
+        <v>2649.68679</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.092929</v>
+        <v>109.449788</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.656284</v>
+        <v>3352.043004</v>
       </c>
       <c r="AD6" t="n">
-        <v>783876429.5461688</v>
+        <v>177870450.9741001</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1477,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>API3USDT</t>
+          <t>RENDERUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>API3</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1492,33 +1488,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>71.09</v>
+        <v>75.19</v>
       </c>
       <c r="I7" t="n">
-        <v>71.09</v>
+        <v>75.19</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>none</t>
@@ -1533,13 +1525,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2911093323545551</v>
+        <v>1.497469842827237</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3012</v>
+        <v>1.625</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.466281057989273</v>
+        <v>8.516375657488062</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1547,40 +1539,40 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.252498264631594</v>
+        <v>1.400156728801228</v>
       </c>
       <c r="T7" t="n">
-        <v>13.26342491690886</v>
+        <v>6.498502423413091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3202202655900106</v>
+        <v>1.64721682710996</v>
       </c>
       <c r="V7" t="n">
-        <v>0.349331198825466</v>
+        <v>1.796963811392684</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7539530749144234</v>
+        <v>1.538816076142645</v>
       </c>
       <c r="X7" t="n">
-        <v>1.507906149828844</v>
+        <v>3.077632152285288</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06640106241700978</v>
+        <v>0.06159531875578146</v>
       </c>
       <c r="Z7" t="n">
-        <v>2640.821808</v>
+        <v>75063.73711</v>
       </c>
       <c r="AA7" t="n">
-        <v>9592.519031</v>
+        <v>92343.20483</v>
       </c>
       <c r="AB7" t="n">
-        <v>23.304</v>
+        <v>5.604882</v>
       </c>
       <c r="AC7" t="n">
-        <v>927.281842</v>
+        <v>11.943868</v>
       </c>
       <c r="AD7" t="n">
-        <v>26058749.37708476</v>
+        <v>844175809.799754</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1595,12 +1587,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KERNELUSDT</t>
+          <t>PENDLEUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KernelDAO</t>
+          <t>Pendle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1610,29 +1602,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_too_early</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>68</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>none</t>
@@ -1647,54 +1643,54 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09270579463148025</v>
+        <v>1.26209230790881</v>
       </c>
       <c r="P8" t="n">
-        <v>0.10349</v>
+        <v>1.251</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.63271984387666</v>
+        <v>-0.8788824588582766</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.08266583788608367</v>
+        <v>1.072206158423346</v>
       </c>
       <c r="T8" t="n">
-        <v>10.82991282832637</v>
+        <v>15.04534559758874</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1019763740946283</v>
+        <v>1.388301538699691</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1112469535577763</v>
+        <v>1.514510769490572</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9233684664427152</v>
+        <v>0.6646573809246809</v>
       </c>
       <c r="X8" t="n">
-        <v>1.846736932885428</v>
+        <v>1.329314761849361</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08694392117083792</v>
+        <v>0.07977662544875246</v>
       </c>
       <c r="Z8" t="n">
-        <v>5336.6864852</v>
+        <v>155851.16775</v>
       </c>
       <c r="AA8" t="n">
-        <v>3999.2202866</v>
+        <v>177096.69783</v>
       </c>
       <c r="AB8" t="n">
-        <v>59.551021</v>
+        <v>8.574628000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>493.86463</v>
+        <v>14.698412</v>
       </c>
       <c r="AD8" t="n">
-        <v>29626729.94201142</v>
+        <v>206777026.3858091</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1709,12 +1705,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACXUSDT</t>
+          <t>GRASSUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Across Protocol</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1724,7 +1720,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1738,10 +1734,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="I9" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1761,13 +1757,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04238542903911852</v>
+        <v>0.3479885886288768</v>
       </c>
       <c r="P9" t="n">
-        <v>0.06044</v>
+        <v>0.3698</v>
       </c>
       <c r="Q9" t="n">
-        <v>42.59617366198769</v>
+        <v>6.267852476732982</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1775,40 +1771,40 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.03114605380369105</v>
+        <v>0.3173136714824733</v>
       </c>
       <c r="T9" t="n">
-        <v>26.51707317874353</v>
+        <v>8.814920416576573</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04662397194303037</v>
+        <v>0.3827874474917645</v>
       </c>
       <c r="V9" t="n">
-        <v>0.05086251484694222</v>
+        <v>0.4175863063546522</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3771155260082077</v>
+        <v>1.134440190883048</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7542310520164148</v>
+        <v>2.268880381766094</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1819535191464709</v>
+        <v>0.1352265043948615</v>
       </c>
       <c r="Z9" t="n">
-        <v>6273.9769681</v>
+        <v>9492.782021999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>4031.2949041</v>
+        <v>8370.114282999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>74.18273000000001</v>
+        <v>35.445818</v>
       </c>
       <c r="AC9" t="n">
-        <v>191.560524</v>
+        <v>101.698411</v>
       </c>
       <c r="AD9" t="n">
-        <v>41763370.21581946</v>
+        <v>89760738.25375111</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1823,12 +1819,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ILVUSDT</t>
+          <t>QUBICUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Illuvium</t>
+          <t>Qubic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1838,33 +1834,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="I10" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>none</t>
@@ -1879,13 +1871,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.761873902329719</v>
+        <v>7.644380136933806e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>3.937</v>
+        <v>8.527e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.655288885728637</v>
+        <v>11.54599650011932</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1893,51 +1885,47 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>3.153853029240997</v>
+        <v>6.498555205273249e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>16.16271275632539</v>
+        <v>14.98911502483381</v>
       </c>
       <c r="U10" t="n">
-        <v>4.138061292562691</v>
+        <v>8.408818150627187e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>4.514248682795662</v>
+        <v>9.173256164320567e-07</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6187080195486644</v>
+        <v>0.6671507946554622</v>
       </c>
       <c r="X10" t="n">
-        <v>1.237416039097327</v>
+        <v>1.334301589310924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2802190803719302</v>
+        <v>0.2808660035108214</v>
       </c>
       <c r="Z10" t="n">
-        <v>1997.5291984</v>
+        <v>2131.9867718336</v>
       </c>
       <c r="AA10" t="n">
-        <v>1249.4687718</v>
+        <v>2588.4123728209</v>
       </c>
       <c r="AB10" t="n">
-        <v>133.306692</v>
+        <v>103.047574</v>
       </c>
       <c r="AC10" t="n">
-        <v>341.442049</v>
+        <v>463.670615</v>
       </c>
       <c r="AD10" t="n">
-        <v>26803537.21574193</v>
+        <v>115789814.7646252</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1945,12 +1933,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TAOUSDT</t>
+          <t>NEXOUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Nexo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1960,7 +1948,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1974,10 +1962,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>64.38</v>
+        <v>66.62</v>
       </c>
       <c r="I11" t="n">
-        <v>64.38</v>
+        <v>66.62</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1985,25 +1973,25 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>186.0996672274983</v>
+        <v>0.873134950940246</v>
       </c>
       <c r="P11" t="n">
-        <v>202.5</v>
+        <v>0.9106</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.812660987971022</v>
+        <v>4.290865807102251</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2011,47 +1999,51 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>153.3617360061835</v>
+        <v>0.7698840064974874</v>
       </c>
       <c r="T11" t="n">
-        <v>17.59161190830837</v>
+        <v>11.82531341020898</v>
       </c>
       <c r="U11" t="n">
-        <v>204.7096339502482</v>
+        <v>0.9604484460342706</v>
       </c>
       <c r="V11" t="n">
-        <v>223.319600672998</v>
+        <v>1.047761941128295</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5684527405517108</v>
+        <v>0.8456435489791625</v>
       </c>
       <c r="X11" t="n">
-        <v>1.136905481103421</v>
+        <v>1.691287097958323</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06427529603717853</v>
+        <v>0.2309849859759106</v>
       </c>
       <c r="Z11" t="n">
-        <v>244710.37458</v>
+        <v>9001.218782</v>
       </c>
       <c r="AA11" t="n">
-        <v>216009.93464</v>
+        <v>13284.796032</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.665575</v>
+        <v>14.572537</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.515084</v>
+        <v>74.89732100000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>2173222161.69613</v>
+        <v>587987760.4424373</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2059,12 +2051,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SPKUSDT</t>
+          <t>BABYUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Babylon</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2074,7 +2066,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2088,10 +2080,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>63.37</v>
+        <v>66.25</v>
       </c>
       <c r="I12" t="n">
-        <v>63.37</v>
+        <v>66.25</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2111,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02068289975236165</v>
+        <v>0.01310331652353565</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02215</v>
+        <v>0.01519</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.093300577791717</v>
+        <v>15.92484980971294</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2125,51 +2117,47 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.0174553083569267</v>
+        <v>0.009988554698595768</v>
       </c>
       <c r="T12" t="n">
-        <v>15.60512033650605</v>
+        <v>23.77078977940639</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02275118972759782</v>
+        <v>0.01441364817588922</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02481947970283398</v>
+        <v>0.01572397982824278</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6408153083322514</v>
+        <v>0.4206843816633902</v>
       </c>
       <c r="X12" t="n">
-        <v>1.281630616664502</v>
+        <v>0.8413687633267793</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09025270758122377</v>
+        <v>0.06576783952646888</v>
       </c>
       <c r="Z12" t="n">
-        <v>667.7698829</v>
+        <v>25220.2776228</v>
       </c>
       <c r="AA12" t="n">
-        <v>264.5112212</v>
+        <v>22097.2948839</v>
       </c>
       <c r="AB12" t="n">
-        <v>3774.819904</v>
+        <v>18.68168</v>
       </c>
       <c r="AC12" t="n">
-        <v>8246.715935</v>
+        <v>37.852116</v>
       </c>
       <c r="AD12" t="n">
-        <v>54561819.69676616</v>
+        <v>43171366.92253447</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2177,12 +2165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BDXUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2192,24 +2180,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>62.98</v>
+        <v>64.8</v>
       </c>
       <c r="I13" t="n">
-        <v>62.98</v>
+        <v>64.8</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -2229,54 +2217,54 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08034176632885151</v>
+        <v>35.02929460884199</v>
       </c>
       <c r="P13" t="n">
-        <v>0.08049000000000001</v>
+        <v>37.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1845038737905647</v>
+        <v>7.395825180288007</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>at_trigger</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.07562980638596428</v>
+        <v>32.76966214399084</v>
       </c>
       <c r="T13" t="n">
-        <v>5.864894634753776</v>
+        <v>6.450693598268408</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08837594296173668</v>
+        <v>38.5322240697262</v>
       </c>
       <c r="V13" t="n">
-        <v>0.09641011959462181</v>
+        <v>42.03515353061039</v>
       </c>
       <c r="W13" t="n">
-        <v>1.705060469585034</v>
+        <v>1.550220894491774</v>
       </c>
       <c r="X13" t="n">
-        <v>3.410120939170061</v>
+        <v>3.100441788983545</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.08694032167919098</v>
+        <v>0.05317734645040155</v>
       </c>
       <c r="Z13" t="n">
-        <v>2032.3301783</v>
+        <v>48172.3554</v>
       </c>
       <c r="AA13" t="n">
-        <v>5157.8649675</v>
+        <v>56372.0511</v>
       </c>
       <c r="AB13" t="n">
-        <v>29.67028</v>
+        <v>5.110629</v>
       </c>
       <c r="AC13" t="n">
-        <v>142.814658</v>
+        <v>10.591744</v>
       </c>
       <c r="AD13" t="n">
-        <v>611832112.1631234</v>
+        <v>9674145697.489784</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2291,12 +2279,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C98USDT</t>
+          <t>PIUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Coin98</t>
+          <t>Pi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2311,19 +2299,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="I14" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -2343,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02603569877209733</v>
+        <v>0.2294446510053902</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02844</v>
+        <v>0.25895</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.234632989683277</v>
+        <v>12.85946256115453</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2357,51 +2345,47 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.02115107894885253</v>
+        <v>0.207910571420656</v>
       </c>
       <c r="T14" t="n">
-        <v>18.76123958109276</v>
+        <v>9.385304686936603</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02863926864930707</v>
+        <v>0.2523891161059292</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0312428385265168</v>
+        <v>0.2753335812064682</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5330138212230833</v>
+        <v>1.065495509583083</v>
       </c>
       <c r="X14" t="n">
-        <v>1.066027642446165</v>
+        <v>2.130991019166163</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2812939521800167</v>
+        <v>0.08104822369309274</v>
       </c>
       <c r="Z14" t="n">
-        <v>8541.604637799999</v>
+        <v>13802.7923236</v>
       </c>
       <c r="AA14" t="n">
-        <v>4426.5792542</v>
+        <v>11573.0444722</v>
       </c>
       <c r="AB14" t="n">
-        <v>62.526226</v>
+        <v>52.276368</v>
       </c>
       <c r="AC14" t="n">
-        <v>221.167324</v>
+        <v>98.90740599999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>28451544.45428425</v>
+        <v>2508970765.894073</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2409,12 +2393,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arweave</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2424,7 +2408,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2438,81 +2422,77 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62.29</v>
+        <v>64.38</v>
       </c>
       <c r="I15" t="n">
-        <v>62.29</v>
+        <v>64.38</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.747800039585285</v>
+        <v>186.0996672274983</v>
       </c>
       <c r="P15" t="n">
-        <v>1.776</v>
+        <v>215.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.613454615861332</v>
+        <v>15.916381374445</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>1.447561622557021</v>
+        <v>153.3617360061835</v>
       </c>
       <c r="T15" t="n">
-        <v>17.17807587986461</v>
+        <v>17.59161190830837</v>
       </c>
       <c r="U15" t="n">
-        <v>1.922580043543814</v>
+        <v>204.7096339502482</v>
       </c>
       <c r="V15" t="n">
-        <v>2.097360047502342</v>
+        <v>223.319600672998</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5821373749851441</v>
+        <v>0.5684527405517108</v>
       </c>
       <c r="X15" t="n">
-        <v>1.164274749970288</v>
+        <v>1.136905481103421</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2252252252252255</v>
+        <v>0.06488691138302502</v>
       </c>
       <c r="Z15" t="n">
-        <v>6798.31157</v>
+        <v>314182.01238</v>
       </c>
       <c r="AA15" t="n">
-        <v>5069.86535</v>
+        <v>262355.03892</v>
       </c>
       <c r="AB15" t="n">
-        <v>42.072514</v>
+        <v>7.061839</v>
       </c>
       <c r="AC15" t="n">
-        <v>251.558271</v>
+        <v>9.038126999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>116450658.6914385</v>
+        <v>2326059086.090872</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2527,12 +2507,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRXUSDT</t>
+          <t>BDXUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2542,24 +2522,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>62.02</v>
+        <v>63.39</v>
       </c>
       <c r="I16" t="n">
-        <v>62.02</v>
+        <v>63.39</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2567,66 +2547,66 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2854626181231336</v>
+        <v>0.08021644370352583</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2895</v>
+        <v>0.08037999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.41432945000346</v>
+        <v>0.2038937266761076</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>at_trigger</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.2754525257892857</v>
+        <v>0.07743592519557023</v>
       </c>
       <c r="T16" t="n">
-        <v>3.506621076925067</v>
+        <v>3.466269981043038</v>
       </c>
       <c r="U16" t="n">
-        <v>0.314008879935447</v>
+        <v>0.08823808807387842</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3425551417477603</v>
+        <v>0.096259732444231</v>
       </c>
       <c r="W16" t="n">
-        <v>2.851748101841944</v>
+        <v>2.884945504732699</v>
       </c>
       <c r="X16" t="n">
-        <v>5.703496203683877</v>
+        <v>5.769891009465392</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.03454828122300536</v>
+        <v>0.08710259441299151</v>
       </c>
       <c r="Z16" t="n">
-        <v>506730.368027</v>
+        <v>1831.552884</v>
       </c>
       <c r="AA16" t="n">
-        <v>587658.9180470001</v>
+        <v>457.3992133</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.977842</v>
+        <v>138.992223</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.039514</v>
+        <v>225.469986</v>
       </c>
       <c r="AD16" t="n">
-        <v>27442241532.3625</v>
+        <v>611548146.3913946</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2641,12 +2621,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GRASSUSDT</t>
+          <t>STABLEUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2670,10 +2650,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>61.6</v>
+        <v>62.4</v>
       </c>
       <c r="I17" t="n">
-        <v>61.6</v>
+        <v>62.4</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2693,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3439335936344511</v>
+        <v>0.0284563871080327</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3478</v>
+        <v>0.028829</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.124172351031882</v>
+        <v>1.309417427281612</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2707,40 +2687,40 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.3143012179209261</v>
+        <v>0.02614468028025506</v>
       </c>
       <c r="T17" t="n">
-        <v>8.615725902314662</v>
+        <v>8.123683512602648</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3783269529978963</v>
+        <v>0.03130202581883598</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4127203123613414</v>
+        <v>0.03414766452963924</v>
       </c>
       <c r="W17" t="n">
-        <v>1.160668307392816</v>
+        <v>1.230968683662596</v>
       </c>
       <c r="X17" t="n">
-        <v>2.321336614785632</v>
+        <v>2.461937367325186</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1438228102977133</v>
+        <v>0.1348664303622403</v>
       </c>
       <c r="Z17" t="n">
-        <v>9984.886712</v>
+        <v>17144.38259349</v>
       </c>
       <c r="AA17" t="n">
-        <v>10031.761935</v>
+        <v>17587.01077857</v>
       </c>
       <c r="AB17" t="n">
-        <v>29.702071</v>
+        <v>21.643602</v>
       </c>
       <c r="AC17" t="n">
-        <v>100.600797</v>
+        <v>65.944323</v>
       </c>
       <c r="AD17" t="n">
-        <v>85118035.11042777</v>
+        <v>598559175.9695891</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2755,12 +2735,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FLOWUSDT</t>
+          <t>TRXUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2770,7 +2750,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | entry_late</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2784,81 +2764,77 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>61.02</v>
+        <v>62.02</v>
       </c>
       <c r="I18" t="n">
-        <v>61.02</v>
+        <v>62.02</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04457447341084035</v>
+        <v>0.2854626181231336</v>
       </c>
       <c r="P18" t="n">
-        <v>0.05418</v>
+        <v>0.2891</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.54938881863182</v>
+        <v>1.274206024165814</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.02892253429689919</v>
+        <v>0.2754525257892857</v>
       </c>
       <c r="T18" t="n">
-        <v>35.11413128693219</v>
+        <v>3.506621076925067</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04903192075192439</v>
+        <v>0.314008879935447</v>
       </c>
       <c r="V18" t="n">
-        <v>0.05348936809300842</v>
+        <v>0.3425551417477603</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2847856299871367</v>
+        <v>2.851748101841944</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5695712599742729</v>
+        <v>5.703496203683877</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.03693444136657282</v>
+        <v>0.03459609064177287</v>
       </c>
       <c r="Z18" t="n">
-        <v>8999.816822799999</v>
+        <v>483021.218046</v>
       </c>
       <c r="AA18" t="n">
-        <v>7755.9362433</v>
+        <v>536944.349084</v>
       </c>
       <c r="AB18" t="n">
-        <v>25.800893</v>
+        <v>3.671689</v>
       </c>
       <c r="AC18" t="n">
-        <v>754.889016</v>
+        <v>6.07642</v>
       </c>
       <c r="AD18" t="n">
-        <v>88847914.46100163</v>
+        <v>27405848047.07561</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2873,12 +2849,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STABLEUSDT</t>
+          <t>FORMUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2893,19 +2869,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>60.8</v>
+        <v>61.25</v>
       </c>
       <c r="I19" t="n">
-        <v>60.8</v>
+        <v>61.25</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2925,13 +2901,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02832775756230391</v>
+        <v>0.2562320299151192</v>
       </c>
       <c r="P19" t="n">
-        <v>0.029201</v>
+        <v>0.2867</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.082638771443458</v>
+        <v>11.89077341149498</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2939,47 +2915,51 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.02599522480157275</v>
+        <v>0.1949738778129414</v>
       </c>
       <c r="T19" t="n">
-        <v>8.234088969453397</v>
+        <v>23.9072968834031</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03116053331853431</v>
+        <v>0.2818552329066311</v>
       </c>
       <c r="V19" t="n">
-        <v>0.03399330907476469</v>
+        <v>0.307478435898143</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214463438165138</v>
+        <v>0.4182823365088255</v>
       </c>
       <c r="X19" t="n">
-        <v>2.428926876330272</v>
+        <v>0.83656467301765</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1198938083411846</v>
+        <v>0.1049134464067223</v>
       </c>
       <c r="Z19" t="n">
-        <v>19597.28000165</v>
+        <v>7990.333059000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>20170.34130185</v>
+        <v>7052.412478</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.049708</v>
+        <v>31.661081</v>
       </c>
       <c r="AC19" t="n">
-        <v>50.151059</v>
+        <v>1466.016537</v>
       </c>
       <c r="AD19" t="n">
-        <v>607368724.4227183</v>
+        <v>110689255.3801944</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2987,12 +2967,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>FLOWUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3002,7 +2982,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3016,15 +2996,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>60.15</v>
+        <v>61.02</v>
       </c>
       <c r="I20" t="n">
-        <v>60.15</v>
+        <v>61.02</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>none</t>
@@ -3039,13 +3023,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5240011855153761</v>
+        <v>0.04457447341084035</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5644</v>
+        <v>0.05593</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.709679978088224</v>
+        <v>25.47540266936284</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3053,40 +3037,40 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.4461252830472255</v>
+        <v>0.02892253429689919</v>
       </c>
       <c r="T20" t="n">
-        <v>14.86177982432549</v>
+        <v>35.11413128693219</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5764013040669138</v>
+        <v>0.04903192075192439</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6288014226184513</v>
+        <v>0.05348936809300842</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6728669189158755</v>
+        <v>0.2847856299871367</v>
       </c>
       <c r="X20" t="n">
-        <v>1.345733837831748</v>
+        <v>0.5695712599742729</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.07089684509040534</v>
+        <v>0.1786671431123868</v>
       </c>
       <c r="Z20" t="n">
-        <v>162590.949339</v>
+        <v>8885.0627276</v>
       </c>
       <c r="AA20" t="n">
-        <v>151866.931798</v>
+        <v>7303.6114379</v>
       </c>
       <c r="AB20" t="n">
-        <v>15.767815</v>
+        <v>35.989171</v>
       </c>
       <c r="AC20" t="n">
-        <v>25.592931</v>
+        <v>884.668048</v>
       </c>
       <c r="AD20" t="n">
-        <v>420712672.5785776</v>
+        <v>91849072.04406074</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3101,12 +3085,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>ETHFIUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>ether.fi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3121,19 +3105,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>60.15</v>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>60.15</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -3153,13 +3137,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>34.26290093783501</v>
+        <v>0.5240011855153761</v>
       </c>
       <c r="P21" t="n">
-        <v>36.52</v>
+        <v>0.5742</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.587588909240827</v>
+        <v>9.579904754461843</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3167,40 +3151,40 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>32.10370623110992</v>
+        <v>0.4461252830472255</v>
       </c>
       <c r="T21" t="n">
-        <v>6.301844407870298</v>
+        <v>14.86177982432549</v>
       </c>
       <c r="U21" t="n">
-        <v>37.68919103161852</v>
+        <v>0.5764013040669138</v>
       </c>
       <c r="V21" t="n">
-        <v>41.11548112540201</v>
+        <v>0.6288014226184513</v>
       </c>
       <c r="W21" t="n">
-        <v>1.586837019890738</v>
+        <v>0.6728669189158755</v>
       </c>
       <c r="X21" t="n">
-        <v>3.17367403978147</v>
+        <v>1.345733837831748</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.05476451259584646</v>
+        <v>0.1394457033292701</v>
       </c>
       <c r="Z21" t="n">
-        <v>73427.9114</v>
+        <v>169614.002871</v>
       </c>
       <c r="AA21" t="n">
-        <v>110666.3722</v>
+        <v>175416.247107</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.300758</v>
+        <v>17.141318</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.758342</v>
+        <v>24.978736</v>
       </c>
       <c r="AD21" t="n">
-        <v>9399894558.150595</v>
+        <v>427857382.9845378</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>

--- a/reports/2026-03-12.xlsx
+++ b/reports/2026-03-12.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-12 17:03 UTC</t>
+          <t>2026-03-12 17:13 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-12_1773334934529</t>
+          <t>2026-03-12_1773335486896</t>
         </is>
       </c>
     </row>
@@ -979,22 +979,22 @@
         <v>1.169138388750603</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03795786676788346</v>
+        <v>0.03798670465336713</v>
       </c>
       <c r="Z2" t="n">
-        <v>20517.44131</v>
+        <v>22546.16453</v>
       </c>
       <c r="AA2" t="n">
-        <v>25619.93872</v>
+        <v>29474.44618</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.398214</v>
+        <v>8.058158000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.382778</v>
+        <v>26.015131</v>
       </c>
       <c r="AD2" t="n">
-        <v>1448939419.602685</v>
+        <v>1447315909.496184</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         <v>0.02835889643807475</v>
       </c>
       <c r="P3" t="n">
-        <v>0.034508</v>
+        <v>0.034414</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.68315532077418</v>
+        <v>21.3516896722245</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1093,22 +1093,22 @@
         <v>0.9797176619559265</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06376996434679609</v>
+        <v>0.05228758169933823</v>
       </c>
       <c r="Z3" t="n">
-        <v>30662.00613367</v>
+        <v>29984.46548389</v>
       </c>
       <c r="AA3" t="n">
-        <v>30653.81337493</v>
+        <v>30344.84639767</v>
       </c>
       <c r="AB3" t="n">
-        <v>35.673139</v>
+        <v>39.077321</v>
       </c>
       <c r="AC3" t="n">
-        <v>53.567102</v>
+        <v>53.000236</v>
       </c>
       <c r="AD3" t="n">
-        <v>169919316.72061</v>
+        <v>169569969.1761453</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         <v>3.761873902329719</v>
       </c>
       <c r="P4" t="n">
-        <v>4.255</v>
+        <v>4.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.10852278607451</v>
+        <v>13.77308519962373</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1211,22 +1211,22 @@
         <v>1.237416039097327</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3054870168017836</v>
+        <v>0.2807674309780172</v>
       </c>
       <c r="Z4" t="n">
-        <v>4615.6894405</v>
+        <v>6181.9337926</v>
       </c>
       <c r="AA4" t="n">
-        <v>1840.3309712</v>
+        <v>2280.1569009</v>
       </c>
       <c r="AB4" t="n">
-        <v>122.504139</v>
+        <v>106.580871</v>
       </c>
       <c r="AC4" t="n">
-        <v>1459.267834</v>
+        <v>1139.870385</v>
       </c>
       <c r="AD4" t="n">
-        <v>29125629.62737596</v>
+        <v>29137027.40677251</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1296,10 +1296,10 @@
         <v>0.02068289975236165</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02307</v>
+        <v>0.02314</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.5414196085623</v>
+        <v>11.87986344786007</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1325,22 +1325,22 @@
         <v>1.281630616664502</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04337453914551982</v>
+        <v>0.04320587599913413</v>
       </c>
       <c r="Z5" t="n">
-        <v>122.2521477</v>
+        <v>673.1298133</v>
       </c>
       <c r="AA5" t="n">
-        <v>600.4083439000001</v>
+        <v>765.2184619</v>
       </c>
       <c r="AB5" t="n">
-        <v>4002.279124</v>
+        <v>3878.743481</v>
       </c>
       <c r="AC5" t="n">
-        <v>10981.199497</v>
+        <v>10871.182133</v>
       </c>
       <c r="AD5" t="n">
-        <v>56821501.96896987</v>
+        <v>56926636.32364494</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1414,10 +1414,10 @@
         <v>17.79485789424142</v>
       </c>
       <c r="P6" t="n">
-        <v>17.87</v>
+        <v>17.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4222686475226167</v>
+        <v>0.3660726382066937</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1443,22 +1443,22 @@
         <v>1.374717988102303</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.05603810591202894</v>
+        <v>0.05594405594404481</v>
       </c>
       <c r="Z6" t="n">
-        <v>6609.15855</v>
+        <v>9707.602930000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>2649.68679</v>
+        <v>2857.83331</v>
       </c>
       <c r="AB6" t="n">
-        <v>109.449788</v>
+        <v>101.015467</v>
       </c>
       <c r="AC6" t="n">
-        <v>3352.043004</v>
+        <v>3161.83812</v>
       </c>
       <c r="AD6" t="n">
-        <v>177870450.9741001</v>
+        <v>177950103.9508288</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1528,10 +1528,10 @@
         <v>1.497469842827237</v>
       </c>
       <c r="P7" t="n">
-        <v>1.625</v>
+        <v>1.634</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.516375657488062</v>
+        <v>9.117389430360291</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1557,22 +1557,22 @@
         <v>3.077632152285288</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06159531875578146</v>
+        <v>0.06110601894287271</v>
       </c>
       <c r="Z7" t="n">
-        <v>75063.73711</v>
+        <v>94762.38460999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>92343.20483</v>
+        <v>128792.8303</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.604882</v>
+        <v>10.174159</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.943868</v>
+        <v>15.853228</v>
       </c>
       <c r="AD7" t="n">
-        <v>844175809.799754</v>
+        <v>844900689.1518819</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         <v>1.26209230790881</v>
       </c>
       <c r="P8" t="n">
-        <v>1.251</v>
+        <v>1.256</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8788824588582766</v>
+        <v>-0.4827149227226046</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1675,22 +1675,22 @@
         <v>1.329314761849361</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07977662544875246</v>
+        <v>0.07964954201514232</v>
       </c>
       <c r="Z8" t="n">
-        <v>155851.16775</v>
+        <v>163371.17196</v>
       </c>
       <c r="AA8" t="n">
-        <v>177096.69783</v>
+        <v>178477.17919</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.574628000000001</v>
+        <v>8.481453999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.698412</v>
+        <v>14.831201</v>
       </c>
       <c r="AD8" t="n">
-        <v>206777026.3858091</v>
+        <v>207582919.5951455</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         <v>0.3479885886288768</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3698</v>
+        <v>0.3668</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.267852476732982</v>
+        <v>5.405755241929833</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1789,22 +1789,22 @@
         <v>2.268880381766094</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1352265043948615</v>
+        <v>0.08166598611677336</v>
       </c>
       <c r="Z9" t="n">
-        <v>9492.782021999999</v>
+        <v>8174.309386</v>
       </c>
       <c r="AA9" t="n">
-        <v>8370.114282999999</v>
+        <v>6704.930666</v>
       </c>
       <c r="AB9" t="n">
-        <v>35.445818</v>
+        <v>50.518637</v>
       </c>
       <c r="AC9" t="n">
-        <v>101.698411</v>
+        <v>121.366258</v>
       </c>
       <c r="AD9" t="n">
-        <v>89760738.25375111</v>
+        <v>89819876.68674217</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         <v>7.644380136933806e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>8.527e-07</v>
+        <v>8.593e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.54599650011932</v>
+        <v>12.40937585616575</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1903,22 +1903,22 @@
         <v>1.334301589310924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2808660035108214</v>
+        <v>0.5023657923944161</v>
       </c>
       <c r="Z10" t="n">
-        <v>2131.9867718336</v>
+        <v>2017.5571348224</v>
       </c>
       <c r="AA10" t="n">
-        <v>2588.4123728209</v>
+        <v>2661.3959954289</v>
       </c>
       <c r="AB10" t="n">
-        <v>103.047574</v>
+        <v>129.728999</v>
       </c>
       <c r="AC10" t="n">
-        <v>463.670615</v>
+        <v>478.513844</v>
       </c>
       <c r="AD10" t="n">
-        <v>115789814.7646252</v>
+        <v>115806040.3121527</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1988,10 +1988,10 @@
         <v>0.873134950940246</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9106</v>
+        <v>0.9091</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.290865807102251</v>
+        <v>4.11907105780438</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2017,22 +2017,22 @@
         <v>1.691287097958323</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2309849859759106</v>
+        <v>0.1979544704717941</v>
       </c>
       <c r="Z11" t="n">
-        <v>9001.218782</v>
+        <v>7443.468533</v>
       </c>
       <c r="AA11" t="n">
-        <v>13284.796032</v>
+        <v>12777.413133</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.572537</v>
+        <v>38.484147</v>
       </c>
       <c r="AC11" t="n">
-        <v>74.89732100000001</v>
+        <v>85.651083</v>
       </c>
       <c r="AD11" t="n">
-        <v>587987760.4424373</v>
+        <v>587950273.060302</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         <v>0.01310331652353565</v>
       </c>
       <c r="P12" t="n">
-        <v>0.01519</v>
+        <v>0.0152</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.92484980971294</v>
+        <v>16.00116636653301</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2135,22 +2135,22 @@
         <v>0.8413687633267793</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.06576783952646888</v>
+        <v>0.06594131223211074</v>
       </c>
       <c r="Z12" t="n">
-        <v>25220.2776228</v>
+        <v>24776.3011452</v>
       </c>
       <c r="AA12" t="n">
-        <v>22097.2948839</v>
+        <v>22704.7280005</v>
       </c>
       <c r="AB12" t="n">
-        <v>18.68168</v>
+        <v>13.66498</v>
       </c>
       <c r="AC12" t="n">
-        <v>37.852116</v>
+        <v>35.881631</v>
       </c>
       <c r="AD12" t="n">
-        <v>43171366.92253447</v>
+        <v>43163284.72810072</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2249,22 +2249,22 @@
         <v>3.100441788983545</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.05317734645040155</v>
+        <v>0.053106744556567</v>
       </c>
       <c r="Z13" t="n">
-        <v>48172.3554</v>
+        <v>65241.8478</v>
       </c>
       <c r="AA13" t="n">
-        <v>56372.0511</v>
+        <v>61032.7959</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.110629</v>
+        <v>6.498058</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.591744</v>
+        <v>12.216332</v>
       </c>
       <c r="AD13" t="n">
-        <v>9674145697.489784</v>
+        <v>9684598961.100435</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         <v>0.2294446510053902</v>
       </c>
       <c r="P14" t="n">
-        <v>0.25895</v>
+        <v>0.26056</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.85946256115453</v>
+        <v>13.56115684469752</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2363,22 +2363,22 @@
         <v>2.130991019166163</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.08104822369309274</v>
+        <v>0.04606525911708598</v>
       </c>
       <c r="Z14" t="n">
-        <v>13802.7923236</v>
+        <v>11590.0638074</v>
       </c>
       <c r="AA14" t="n">
-        <v>11573.0444722</v>
+        <v>18937.819493</v>
       </c>
       <c r="AB14" t="n">
-        <v>52.276368</v>
+        <v>33.409059</v>
       </c>
       <c r="AC14" t="n">
-        <v>98.90740599999999</v>
+        <v>70.840422</v>
       </c>
       <c r="AD14" t="n">
-        <v>2508970765.894073</v>
+        <v>2512071813.031233</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>186.0996672274983</v>
       </c>
       <c r="P15" t="n">
-        <v>215.72</v>
+        <v>216</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.916381374445</v>
+        <v>16.06683838716909</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2477,22 +2477,22 @@
         <v>1.136905481103421</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.06488691138302502</v>
+        <v>0.01852023335493659</v>
       </c>
       <c r="Z15" t="n">
-        <v>314182.01238</v>
+        <v>210050.09351</v>
       </c>
       <c r="AA15" t="n">
-        <v>262355.03892</v>
+        <v>274761.61358</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.061839</v>
+        <v>5.940529</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.038126999999999</v>
+        <v>8.784697</v>
       </c>
       <c r="AD15" t="n">
-        <v>2326059086.090872</v>
+        <v>2325482295.064912</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_late</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2562,14 +2562,14 @@
         <v>0.08021644370352583</v>
       </c>
       <c r="P16" t="n">
-        <v>0.08037999999999999</v>
+        <v>0.08046</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2038937266761076</v>
+        <v>0.3036239020696829</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>at_trigger</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2591,22 +2591,22 @@
         <v>5.769891009465392</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.08710259441299151</v>
+        <v>0.09939122872407828</v>
       </c>
       <c r="Z16" t="n">
-        <v>1831.552884</v>
+        <v>2908.5661379</v>
       </c>
       <c r="AA16" t="n">
-        <v>457.3992133</v>
+        <v>4085.2073075</v>
       </c>
       <c r="AB16" t="n">
-        <v>138.992223</v>
+        <v>64.995886</v>
       </c>
       <c r="AC16" t="n">
-        <v>225.469986</v>
+        <v>150.558471</v>
       </c>
       <c r="AD16" t="n">
-        <v>611548146.3913946</v>
+        <v>611286646.254997</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         <v>0.0284563871080327</v>
       </c>
       <c r="P17" t="n">
-        <v>0.028829</v>
+        <v>0.028676</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.309417427281612</v>
+        <v>0.7717525458645014</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2705,22 +2705,22 @@
         <v>2.461937367325186</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1348664303622403</v>
+        <v>0.05579967915184018</v>
       </c>
       <c r="Z17" t="n">
-        <v>17144.38259349</v>
+        <v>14753.03545099</v>
       </c>
       <c r="AA17" t="n">
-        <v>17587.01077857</v>
+        <v>18158.6338473</v>
       </c>
       <c r="AB17" t="n">
-        <v>21.643602</v>
+        <v>22.218777</v>
       </c>
       <c r="AC17" t="n">
-        <v>65.944323</v>
+        <v>62.717224</v>
       </c>
       <c r="AD17" t="n">
-        <v>598559175.9695891</v>
+        <v>596487857.2919275</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
         <v>0.2854626181231336</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2891</v>
+        <v>0.2893</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.274206024165814</v>
+        <v>1.344267737084626</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2819,22 +2819,22 @@
         <v>5.703496203683877</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.03459609064177287</v>
+        <v>0.06915629322267565</v>
       </c>
       <c r="Z18" t="n">
-        <v>483021.218046</v>
+        <v>471263.91101</v>
       </c>
       <c r="AA18" t="n">
-        <v>536944.349084</v>
+        <v>499620.23694</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.671689</v>
+        <v>5.760316</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.07642</v>
+        <v>8.041582999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>27405848047.07561</v>
+        <v>27403780603.78295</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
         <v>0.2562320299151192</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2867</v>
+        <v>0.2856</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.89077341149498</v>
+        <v>11.46147501333436</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2933,22 +2933,22 @@
         <v>0.83656467301765</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1049134464067223</v>
+        <v>0.1048034934497701</v>
       </c>
       <c r="Z19" t="n">
-        <v>7990.333059000001</v>
+        <v>10884.128622</v>
       </c>
       <c r="AA19" t="n">
-        <v>7052.412478</v>
+        <v>6008.188212</v>
       </c>
       <c r="AB19" t="n">
-        <v>31.661081</v>
+        <v>31.41547</v>
       </c>
       <c r="AC19" t="n">
-        <v>1466.016537</v>
+        <v>2185.347063</v>
       </c>
       <c r="AD19" t="n">
-        <v>110689255.3801944</v>
+        <v>109671678.5561815</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         <v>0.04457447341084035</v>
       </c>
       <c r="P20" t="n">
-        <v>0.05593</v>
+        <v>0.05591</v>
       </c>
       <c r="Q20" t="n">
-        <v>25.47540266936284</v>
+        <v>25.43053393964019</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3055,22 +3055,22 @@
         <v>0.5695712599742729</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1786671431123868</v>
+        <v>0.07160759040457997</v>
       </c>
       <c r="Z20" t="n">
-        <v>8885.0627276</v>
+        <v>13422.4692328</v>
       </c>
       <c r="AA20" t="n">
-        <v>7303.6114379</v>
+        <v>10519.3794967</v>
       </c>
       <c r="AB20" t="n">
-        <v>35.989171</v>
+        <v>24.973264</v>
       </c>
       <c r="AC20" t="n">
-        <v>884.668048</v>
+        <v>285.101018</v>
       </c>
       <c r="AD20" t="n">
-        <v>91849072.04406074</v>
+        <v>92342793.0864584</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         <v>0.5240011855153761</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5742</v>
+        <v>0.5728</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.579904754461843</v>
+        <v>9.312729786408447</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3169,22 +3169,22 @@
         <v>1.345733837831748</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1394457033292701</v>
+        <v>0.104785190359751</v>
       </c>
       <c r="Z21" t="n">
-        <v>169614.002871</v>
+        <v>195790.36019</v>
       </c>
       <c r="AA21" t="n">
-        <v>175416.247107</v>
+        <v>173664.396072</v>
       </c>
       <c r="AB21" t="n">
-        <v>17.141318</v>
+        <v>14.26032</v>
       </c>
       <c r="AC21" t="n">
-        <v>24.978736</v>
+        <v>23.466074</v>
       </c>
       <c r="AD21" t="n">
-        <v>427857382.9845378</v>
+        <v>427138118.9722112</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
